--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:18</t>
+    <t xml:space="preserve">2026-09-09 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:13</t>
+    <t xml:space="preserve">2026-09-17 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:09</t>
+    <t xml:space="preserve">2026-09-23 12:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:38</t>
+    <t xml:space="preserve">2026-10-02 14:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:21</t>
+    <t xml:space="preserve">2026-10-05 11:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>588427.62</v>
+        <v>588427.63</v>
       </c>
     </row>
     <row r="3">
@@ -826,7 +826,7 @@
         <v>2024</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>316240.12</v>
+        <v>316240.13</v>
       </c>
     </row>
     <row r="18">
@@ -843,7 +843,7 @@
         <v>2024</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>304849.12</v>
+        <v>304849.13</v>
       </c>
     </row>
     <row r="19">
@@ -894,7 +894,7 @@
         <v>2024</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>289081.62</v>
+        <v>289081.63</v>
       </c>
     </row>
     <row r="22">
